--- a/Result/checksun/電器電纜.xlsx
+++ b/Result/checksun/電器電纜.xlsx
@@ -1013,7 +1013,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -1301,7 +1305,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -1589,7 +1597,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -1877,7 +1889,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -2165,7 +2181,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -2453,7 +2473,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -2741,7 +2765,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -3029,7 +3057,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -3317,7 +3349,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -3605,7 +3641,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -4185,7 +4225,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -4473,7 +4517,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -4761,7 +4809,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -5049,7 +5101,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -5337,7 +5393,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -5625,7 +5685,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -5913,7 +5977,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -6201,7 +6269,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -6489,7 +6561,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -6777,7 +6853,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -7357,7 +7437,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -7645,7 +7729,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -7933,7 +8021,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -8221,7 +8313,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -8509,7 +8605,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -8797,7 +8897,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -9085,7 +9189,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -9373,7 +9481,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -9661,7 +9773,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -9949,7 +10065,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -10529,7 +10649,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -10817,7 +10941,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -11105,7 +11233,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -11393,7 +11525,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -11681,7 +11817,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -11969,7 +12109,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -12257,7 +12401,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -12545,7 +12693,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -12833,7 +12985,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -13121,7 +13277,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -13701,7 +13861,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -13989,7 +14153,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -14277,7 +14445,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -14565,7 +14737,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -14853,7 +15029,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -15141,7 +15321,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -15429,7 +15613,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -15717,7 +15905,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -16005,7 +16197,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -16293,7 +16489,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -16873,7 +17073,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -17161,7 +17365,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -17449,7 +17657,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -17737,7 +17949,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -18025,7 +18241,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -18313,7 +18533,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -18601,7 +18825,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -18889,7 +19117,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -19177,7 +19409,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -19465,7 +19701,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -20045,7 +20285,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -20333,7 +20577,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -20621,7 +20869,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -20909,7 +21161,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -21197,7 +21453,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -21485,7 +21745,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -21773,7 +22037,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -22061,7 +22329,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -22349,7 +22621,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -22637,7 +22913,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -23217,7 +23497,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -23505,7 +23789,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -23793,7 +24081,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -24081,7 +24373,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -24369,7 +24665,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -24657,7 +24957,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -24945,7 +25249,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -25233,7 +25541,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -25521,7 +25833,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -25809,7 +26125,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -26389,7 +26709,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -26677,7 +27001,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -26965,7 +27293,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -27253,7 +27585,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -27541,7 +27877,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -27829,7 +28169,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -28117,7 +28461,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -28405,7 +28753,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -28693,7 +29045,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -28981,7 +29337,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -29561,7 +29921,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -29849,7 +30213,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -30137,7 +30505,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -30425,7 +30797,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -30713,7 +31089,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -31001,7 +31381,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -31289,7 +31673,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -31577,7 +31965,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -31865,7 +32257,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -32153,7 +32549,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -32733,7 +33133,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -33021,7 +33425,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -33309,7 +33717,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -33597,7 +34009,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -33885,7 +34301,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -34173,7 +34593,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -34461,7 +34885,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -34749,7 +35177,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -35037,7 +35469,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr"/>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -35325,7 +35761,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -35905,7 +36345,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -36193,7 +36637,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -36481,7 +36929,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -36769,7 +37221,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -37057,7 +37513,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr"/>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -37345,7 +37805,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -37633,7 +38097,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -37921,7 +38389,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr"/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -38209,7 +38681,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr"/>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -38497,7 +38973,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -39077,7 +39557,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -39365,7 +39849,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -39653,7 +40141,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr"/>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -39941,7 +40433,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr"/>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -40229,7 +40725,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -40517,7 +41017,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -40805,7 +41309,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -41093,7 +41601,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr"/>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -41381,7 +41893,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr"/>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -41669,7 +42185,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -42249,7 +42769,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr"/>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -42537,7 +43061,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr"/>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -42825,7 +43353,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr"/>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -43113,7 +43645,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr"/>
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -43401,7 +43937,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr"/>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -43689,7 +44229,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr"/>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -43977,7 +44521,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr"/>
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -44265,7 +44813,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr"/>
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -44553,7 +45105,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr"/>
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -44841,7 +45397,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr"/>
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -45421,7 +45981,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr"/>
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -45709,7 +46273,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr"/>
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -45997,7 +46565,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr"/>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -46285,7 +46857,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr"/>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -46573,7 +47149,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr"/>
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -46861,7 +47441,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr"/>
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -47149,7 +47733,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr"/>
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -47437,7 +48025,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr"/>
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -47725,7 +48317,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr"/>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -48013,7 +48609,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr"/>
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -48593,7 +49193,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr"/>
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -48881,7 +49485,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr"/>
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -49169,7 +49777,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr"/>
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -49457,7 +50069,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr"/>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -49745,7 +50361,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr"/>
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -50033,7 +50653,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr"/>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -50321,7 +50945,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr"/>
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -50609,7 +51237,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr"/>
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -50897,7 +51529,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr"/>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -51185,7 +51821,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr"/>
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>2025-08-25</t>

--- a/Result/checksun/電器電纜.xlsx
+++ b/Result/checksun/電器電纜.xlsx
@@ -1011,15 +1011,11 @@
           <t>68.845</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>70.286</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>72.215</t>
-        </is>
+      <c r="AN2" t="n">
+        <v>70.286</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>72.215</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -1398,15 +1394,11 @@
           <t>69.075</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>70.47399999999999</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>72.415</t>
-        </is>
+      <c r="AN3" t="n">
+        <v>70.47399999999999</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>72.41500000000001</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -1785,15 +1777,11 @@
           <t>68.83000000000001</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>70.482</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>72.49</t>
-        </is>
+      <c r="AN4" t="n">
+        <v>70.482</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>72.48999999999999</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -2172,15 +2160,11 @@
           <t>68.58500000000001</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>70.532</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>72.58375</t>
-        </is>
+      <c r="AN5" t="n">
+        <v>70.532</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>72.58374999999999</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -2559,15 +2543,11 @@
           <t>68.35999999999999</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>70.586</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>72.66624999999999</t>
-        </is>
+      <c r="AN6" t="n">
+        <v>70.586</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>72.66624999999999</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -2946,15 +2926,11 @@
           <t>68.10499999999999</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>70.64200000000001</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>72.73875000000001</t>
-        </is>
+      <c r="AN7" t="n">
+        <v>70.64200000000001</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>72.73875000000001</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -3333,15 +3309,11 @@
           <t>67.79499999999999</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>70.69800000000001</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>72.8</t>
-        </is>
+      <c r="AN8" t="n">
+        <v>70.69800000000001</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>72.8</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -3720,15 +3692,11 @@
           <t>67.515</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>70.778</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>72.89125</t>
-        </is>
+      <c r="AN9" t="n">
+        <v>70.77800000000001</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>72.89125</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -4107,15 +4075,11 @@
           <t>67.33</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>70.882</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>73.00500000000001</t>
-        </is>
+      <c r="AN10" t="n">
+        <v>70.88200000000001</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>73.00500000000001</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -4494,15 +4458,11 @@
           <t>67.325</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>71.05199999999999</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>73.15375</t>
-        </is>
+      <c r="AN11" t="n">
+        <v>71.05199999999999</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>73.15375</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -4881,15 +4841,11 @@
           <t>22.8775</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>23.334</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>23.24375</t>
-        </is>
+      <c r="AN12" t="n">
+        <v>23.334</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>23.24375</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -5268,15 +5224,11 @@
           <t>22.8975</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>23.349</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>23.245625</t>
-        </is>
+      <c r="AN13" t="n">
+        <v>23.349</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>23.245625</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -5655,15 +5607,11 @@
           <t>22.91</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>23.361</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>23.251875</t>
-        </is>
+      <c r="AN14" t="n">
+        <v>23.361</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>23.251875</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -6042,15 +5990,11 @@
           <t>22.9375</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>23.366</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>23.263125</t>
-        </is>
+      <c r="AN15" t="n">
+        <v>23.366</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>23.263125</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -6429,15 +6373,11 @@
           <t>22.9575</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>23.377</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>23.2725</t>
-        </is>
+      <c r="AN16" t="n">
+        <v>23.377</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>23.2725</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -6816,15 +6756,11 @@
           <t>22.9775</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>23.388</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>23.28125</t>
-        </is>
+      <c r="AN17" t="n">
+        <v>23.388</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>23.28125</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -7203,15 +7139,11 @@
           <t>23.0025</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>23.387</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>23.285625</t>
-        </is>
+      <c r="AN18" t="n">
+        <v>23.387</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>23.285625</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -7590,15 +7522,11 @@
           <t>23.0225</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>23.389</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>23.2925</t>
-        </is>
+      <c r="AN19" t="n">
+        <v>23.389</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>23.2925</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -7977,15 +7905,11 @@
           <t>23.06</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>23.395</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>23.298125</t>
-        </is>
+      <c r="AN20" t="n">
+        <v>23.395</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>23.298125</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -8364,15 +8288,11 @@
           <t>23.0925</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>23.398</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>23.298125</t>
-        </is>
+      <c r="AN21" t="n">
+        <v>23.398</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>23.298125</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -8751,15 +8671,11 @@
           <t>19.6075</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>18.502</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>18.2275</t>
-        </is>
+      <c r="AN22" t="n">
+        <v>18.502</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>18.2275</v>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
@@ -9138,15 +9054,11 @@
           <t>19.645</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>18.462</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>18.20625</t>
-        </is>
+      <c r="AN23" t="n">
+        <v>18.462</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>18.20625</v>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
@@ -9525,15 +9437,11 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>18.42</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>18.18625</t>
-        </is>
+      <c r="AN24" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>18.18625</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -9912,15 +9820,11 @@
           <t>19.58</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>18.383</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>18.164375</t>
-        </is>
+      <c r="AN25" t="n">
+        <v>18.383</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>18.164375</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -10299,15 +10203,11 @@
           <t>19.465</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>18.344</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>18.139375</t>
-        </is>
+      <c r="AN26" t="n">
+        <v>18.344</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>18.139375</v>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
@@ -10686,15 +10586,11 @@
           <t>19.325</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>18.3</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>18.110625</t>
-        </is>
+      <c r="AN27" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>18.110625</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -11073,15 +10969,11 @@
           <t>19.2</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>18.266</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>18.089375</t>
-        </is>
+      <c r="AN28" t="n">
+        <v>18.266</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>18.089375</v>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
@@ -11460,15 +11352,11 @@
           <t>19.065</t>
         </is>
       </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>18.229</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>18.0675</t>
-        </is>
+      <c r="AN29" t="n">
+        <v>18.229</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>18.0675</v>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
@@ -11847,15 +11735,11 @@
           <t>18.9475</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>18.196</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>18.05125</t>
-        </is>
+      <c r="AN30" t="n">
+        <v>18.196</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>18.05125</v>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -12234,15 +12118,11 @@
           <t>18.855</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>18.177</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>18.046875</t>
-        </is>
+      <c r="AN31" t="n">
+        <v>18.177</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>18.046875</v>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
@@ -12621,15 +12501,11 @@
           <t>11.87</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>11.999</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>11.945625</t>
-        </is>
+      <c r="AN32" t="n">
+        <v>11.999</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>11.945625</v>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -13008,15 +12884,11 @@
           <t>11.845</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>11.989</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>11.9225</t>
-        </is>
+      <c r="AN33" t="n">
+        <v>11.989</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>11.9225</v>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
@@ -13395,15 +13267,11 @@
           <t>11.81</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>11.982</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>11.900625</t>
-        </is>
+      <c r="AN34" t="n">
+        <v>11.982</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>11.900625</v>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
@@ -13782,15 +13650,11 @@
           <t>11.7875</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>11.982</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>11.885</t>
-        </is>
+      <c r="AN35" t="n">
+        <v>11.982</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>11.885</v>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
@@ -14169,15 +14033,11 @@
           <t>11.795</t>
         </is>
       </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>11.993</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>11.878125</t>
-        </is>
+      <c r="AN36" t="n">
+        <v>11.993</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>11.878125</v>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
@@ -14556,15 +14416,11 @@
           <t>11.795</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>11.998</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>11.86875</t>
-        </is>
+      <c r="AN37" t="n">
+        <v>11.998</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>11.86875</v>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
@@ -14943,15 +14799,11 @@
           <t>11.805</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>12.009</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>11.860625</t>
-        </is>
+      <c r="AN38" t="n">
+        <v>12.009</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>11.860625</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
@@ -15330,15 +15182,11 @@
           <t>11.8175</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>12.006</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>11.854375</t>
-        </is>
+      <c r="AN39" t="n">
+        <v>12.006</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>11.854375</v>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
@@ -15717,15 +15565,11 @@
           <t>11.8425</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>12.007</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>11.85</t>
-        </is>
+      <c r="AN40" t="n">
+        <v>12.007</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>11.85</v>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
@@ -16104,15 +15948,11 @@
           <t>11.875</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>12.012</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>11.8475</t>
-        </is>
+      <c r="AN41" t="n">
+        <v>12.012</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>11.8475</v>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
@@ -16491,15 +16331,11 @@
           <t>44.7975</t>
         </is>
       </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>46.122</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>47.5375</t>
-        </is>
+      <c r="AN42" t="n">
+        <v>46.122</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>47.5375</v>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
@@ -16878,15 +16714,11 @@
           <t>44.88</t>
         </is>
       </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>46.163</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>47.586875</t>
-        </is>
+      <c r="AN43" t="n">
+        <v>46.163</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>47.586875</v>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
@@ -17265,15 +17097,11 @@
           <t>44.945</t>
         </is>
       </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>46.235</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>47.63625</t>
-        </is>
+      <c r="AN44" t="n">
+        <v>46.235</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>47.63625</v>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
@@ -17652,15 +17480,11 @@
           <t>45.0925</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>46.318</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>47.69750000000001</t>
-        </is>
+      <c r="AN45" t="n">
+        <v>46.318</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>47.69750000000001</v>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
@@ -18039,15 +17863,11 @@
           <t>45.2025</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>46.369</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>47.74187500000001</t>
-        </is>
+      <c r="AN46" t="n">
+        <v>46.369</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>47.74187500000001</v>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
@@ -18426,15 +18246,11 @@
           <t>45.325</t>
         </is>
       </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>46.479</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>47.785</t>
-        </is>
+      <c r="AN47" t="n">
+        <v>46.479</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>47.785</v>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
@@ -18813,15 +18629,11 @@
           <t>45.4525</t>
         </is>
       </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>46.582</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>47.824375</t>
-        </is>
+      <c r="AN48" t="n">
+        <v>46.582</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>47.824375</v>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
@@ -19200,15 +19012,11 @@
           <t>45.5275</t>
         </is>
       </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>46.724</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>47.8725</t>
-        </is>
+      <c r="AN49" t="n">
+        <v>46.724</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>47.8725</v>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
@@ -19587,15 +19395,11 @@
           <t>45.61499999999999</t>
         </is>
       </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>46.873</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>47.90625</t>
-        </is>
+      <c r="AN50" t="n">
+        <v>46.873</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>47.90625</v>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
@@ -19974,15 +19778,11 @@
           <t>45.71</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>47.026</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>47.94</t>
-        </is>
+      <c r="AN51" t="n">
+        <v>47.026</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>47.94</v>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
@@ -20361,15 +20161,11 @@
           <t>15.5025</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>15.386</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>15.47875</t>
-        </is>
+      <c r="AN52" t="n">
+        <v>15.386</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>15.47875</v>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
@@ -20748,15 +20544,11 @@
           <t>15.54</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>15.401</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>15.486875</t>
-        </is>
+      <c r="AN53" t="n">
+        <v>15.401</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>15.486875</v>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
@@ -21135,15 +20927,11 @@
           <t>15.57</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>15.411</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>15.4975</t>
-        </is>
+      <c r="AN54" t="n">
+        <v>15.411</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>15.4975</v>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
@@ -21522,15 +21310,11 @@
           <t>15.61</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>15.415</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>15.510625</t>
-        </is>
+      <c r="AN55" t="n">
+        <v>15.415</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>15.510625</v>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
@@ -21909,15 +21693,11 @@
           <t>15.5625</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>15.412</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>15.52</t>
-        </is>
+      <c r="AN56" t="n">
+        <v>15.412</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>15.52</v>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
@@ -22296,15 +22076,11 @@
           <t>15.5</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>15.407</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>15.52875</t>
-        </is>
+      <c r="AN57" t="n">
+        <v>15.407</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>15.52875</v>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
@@ -22683,15 +22459,11 @@
           <t>15.46</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>15.412</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>15.540625</t>
-        </is>
+      <c r="AN58" t="n">
+        <v>15.412</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>15.540625</v>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
@@ -23070,15 +22842,11 @@
           <t>15.415</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>15.417</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>15.555625</t>
-        </is>
+      <c r="AN59" t="n">
+        <v>15.417</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>15.555625</v>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
@@ -23457,15 +23225,11 @@
           <t>15.3825</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>15.43</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>15.575625</t>
-        </is>
+      <c r="AN60" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>15.575625</v>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
@@ -23844,15 +23608,11 @@
           <t>15.3475</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>15.436</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>15.591875</t>
-        </is>
+      <c r="AN61" t="n">
+        <v>15.436</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>15.591875</v>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
@@ -24231,15 +23991,11 @@
           <t>35.4225</t>
         </is>
       </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>36.276</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>35.861875</t>
-        </is>
+      <c r="AN62" t="n">
+        <v>36.276</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>35.861875</v>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
@@ -24618,15 +24374,11 @@
           <t>35.4675</t>
         </is>
       </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>36.371</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>35.8775</t>
-        </is>
+      <c r="AN63" t="n">
+        <v>36.371</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>35.8775</v>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
@@ -25005,15 +24757,11 @@
           <t>35.4425</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>36.45399999999999</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>35.898125</t>
-        </is>
+      <c r="AN64" t="n">
+        <v>36.45399999999999</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>35.898125</v>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
@@ -25392,15 +25140,11 @@
           <t>35.47</t>
         </is>
       </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>36.54600000000001</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>35.9425</t>
-        </is>
+      <c r="AN65" t="n">
+        <v>36.54600000000001</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>35.9425</v>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
@@ -25779,15 +25523,11 @@
           <t>35.45</t>
         </is>
       </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>36.593</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>35.988125</t>
-        </is>
+      <c r="AN66" t="n">
+        <v>36.593</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>35.988125</v>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
@@ -26166,15 +25906,11 @@
           <t>35.4675</t>
         </is>
       </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>36.66</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>36.03875000000001</t>
-        </is>
+      <c r="AN67" t="n">
+        <v>36.66</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>36.03875000000001</v>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
@@ -26553,15 +26289,11 @@
           <t>35.52999999999999</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>36.77200000000001</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>36.10375</t>
-        </is>
+      <c r="AN68" t="n">
+        <v>36.77200000000001</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>36.10375</v>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
@@ -26940,15 +26672,11 @@
           <t>35.4925</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>36.839</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>36.165625</t>
-        </is>
+      <c r="AN69" t="n">
+        <v>36.839</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>36.165625</v>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
@@ -27327,15 +27055,11 @@
           <t>35.425</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>36.898</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>36.218125</t>
-        </is>
+      <c r="AN70" t="n">
+        <v>36.898</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>36.218125</v>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
@@ -27714,15 +27438,11 @@
           <t>35.3625</t>
         </is>
       </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>36.985</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>36.2975</t>
-        </is>
+      <c r="AN71" t="n">
+        <v>36.985</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>36.2975</v>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
@@ -28101,15 +27821,11 @@
           <t>46.535</t>
         </is>
       </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>48.43900000000001</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>49.795625</t>
-        </is>
+      <c r="AN72" t="n">
+        <v>48.43900000000001</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>49.795625</v>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
@@ -28488,15 +28204,11 @@
           <t>46.655</t>
         </is>
       </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>48.53</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>49.8525</t>
-        </is>
+      <c r="AN73" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>49.8525</v>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
@@ -28875,15 +28587,11 @@
           <t>46.7975</t>
         </is>
       </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>48.622</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>49.92375</t>
-        </is>
+      <c r="AN74" t="n">
+        <v>48.622</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>49.92375</v>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
@@ -29262,15 +28970,11 @@
           <t>46.9625</t>
         </is>
       </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>48.794</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
+      <c r="AN75" t="n">
+        <v>48.794</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>50</v>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
@@ -29649,15 +29353,11 @@
           <t>47.085</t>
         </is>
       </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>48.957</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>50.070625</t>
-        </is>
+      <c r="AN76" t="n">
+        <v>48.957</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>50.070625</v>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
@@ -30036,15 +29736,11 @@
           <t>47.1725</t>
         </is>
       </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>49.085</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>50.135625</t>
-        </is>
+      <c r="AN77" t="n">
+        <v>49.085</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>50.135625</v>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
@@ -30423,15 +30119,11 @@
           <t>47.375</t>
         </is>
       </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>49.23099999999999</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>50.204375</t>
-        </is>
+      <c r="AN78" t="n">
+        <v>49.23099999999999</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>50.204375</v>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
@@ -30810,15 +30502,11 @@
           <t>47.57000000000001</t>
         </is>
       </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>49.38099999999999</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>50.275625</t>
-        </is>
+      <c r="AN79" t="n">
+        <v>49.38099999999999</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>50.275625</v>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
@@ -31197,15 +30885,11 @@
           <t>47.7775</t>
         </is>
       </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>49.528</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>50.34625</t>
-        </is>
+      <c r="AN80" t="n">
+        <v>49.528</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>50.34625</v>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
@@ -31584,15 +31268,11 @@
           <t>47.985</t>
         </is>
       </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>49.67</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>50.41375</t>
-        </is>
+      <c r="AN81" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>50.41375</v>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
@@ -31971,15 +31651,11 @@
           <t>36.1225</t>
         </is>
       </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>36.785</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>37.33624999999999</t>
-        </is>
+      <c r="AN82" t="n">
+        <v>36.785</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>37.33624999999999</v>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
@@ -32358,15 +32034,11 @@
           <t>36.21749999999999</t>
         </is>
       </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>36.83600000000001</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>37.38312499999999</t>
-        </is>
+      <c r="AN83" t="n">
+        <v>36.83600000000001</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>37.38312499999999</v>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
@@ -32745,15 +32417,11 @@
           <t>36.30249999999999</t>
         </is>
       </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>36.892</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>37.428125</t>
-        </is>
+      <c r="AN84" t="n">
+        <v>36.892</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>37.428125</v>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
@@ -33132,15 +32800,11 @@
           <t>36.3925</t>
         </is>
       </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>36.944</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>37.473125</t>
-        </is>
+      <c r="AN85" t="n">
+        <v>36.944</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>37.473125</v>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
@@ -33519,15 +33183,11 @@
           <t>36.485</t>
         </is>
       </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>36.991</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>37.518125</t>
-        </is>
+      <c r="AN86" t="n">
+        <v>36.991</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>37.518125</v>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
@@ -33906,15 +33566,11 @@
           <t>36.55</t>
         </is>
       </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>37.034</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>37.5625</t>
-        </is>
+      <c r="AN87" t="n">
+        <v>37.034</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>37.5625</v>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
@@ -34293,15 +33949,11 @@
           <t>36.6275</t>
         </is>
       </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>37.082</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>37.603125</t>
-        </is>
+      <c r="AN88" t="n">
+        <v>37.082</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>37.603125</v>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
@@ -34680,15 +34332,11 @@
           <t>36.6875</t>
         </is>
       </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>37.124</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>37.6425</t>
-        </is>
+      <c r="AN89" t="n">
+        <v>37.124</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>37.6425</v>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
@@ -35067,15 +34715,11 @@
           <t>36.7725</t>
         </is>
       </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>37.175</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>37.686875</t>
-        </is>
+      <c r="AN90" t="n">
+        <v>37.175</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>37.686875</v>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
@@ -35454,15 +35098,11 @@
           <t>36.8475</t>
         </is>
       </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>37.226</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>37.729375</t>
-        </is>
+      <c r="AN91" t="n">
+        <v>37.226</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>37.729375</v>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
@@ -35841,15 +35481,11 @@
           <t>38.6875</t>
         </is>
       </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>37.591</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>37.18375</t>
-        </is>
+      <c r="AN92" t="n">
+        <v>37.591</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>37.18375</v>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
@@ -36228,15 +35864,11 @@
           <t>38.635</t>
         </is>
       </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>37.571</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>37.14375</t>
-        </is>
+      <c r="AN93" t="n">
+        <v>37.571</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>37.14375</v>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
@@ -36615,15 +36247,11 @@
           <t>38.52249999999999</t>
         </is>
       </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>37.549</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>37.11</t>
-        </is>
+      <c r="AN94" t="n">
+        <v>37.549</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>37.11</v>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
@@ -37002,15 +36630,11 @@
           <t>38.46749999999999</t>
         </is>
       </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>37.535</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
+      <c r="AN95" t="n">
+        <v>37.535</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>37.1</v>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
@@ -37389,15 +37013,11 @@
           <t>38.3275</t>
         </is>
       </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>37.486</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>37.08499999999999</t>
-        </is>
+      <c r="AN96" t="n">
+        <v>37.486</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>37.08499999999999</v>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
@@ -37776,15 +37396,11 @@
           <t>38.1875</t>
         </is>
       </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>37.44</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>37.070625</t>
-        </is>
+      <c r="AN97" t="n">
+        <v>37.44</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>37.070625</v>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
@@ -38163,15 +37779,11 @@
           <t>38.065</t>
         </is>
       </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>37.41</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>37.060625</t>
-        </is>
+      <c r="AN98" t="n">
+        <v>37.41</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>37.060625</v>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
@@ -38550,15 +38162,11 @@
           <t>37.92</t>
         </is>
       </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>37.385</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>37.055</t>
-        </is>
+      <c r="AN99" t="n">
+        <v>37.385</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>37.055</v>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
@@ -38937,15 +38545,11 @@
           <t>37.7475</t>
         </is>
       </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>37.357</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>37.043125</t>
-        </is>
+      <c r="AN100" t="n">
+        <v>37.357</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>37.043125</v>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
@@ -39324,15 +38928,11 @@
           <t>37.61749999999999</t>
         </is>
       </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>37.343</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>37.040625</t>
-        </is>
+      <c r="AN101" t="n">
+        <v>37.343</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>37.040625</v>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
@@ -39711,15 +39311,11 @@
           <t>12.985</t>
         </is>
       </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>13.029</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>12.96875</t>
-        </is>
+      <c r="AN102" t="n">
+        <v>13.029</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>12.96875</v>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
@@ -40098,15 +39694,11 @@
           <t>13.0025</t>
         </is>
       </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>13.046</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>12.9675</t>
-        </is>
+      <c r="AN103" t="n">
+        <v>13.046</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>12.9675</v>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
@@ -40485,15 +40077,11 @@
           <t>13.0075</t>
         </is>
       </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>13.062</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>12.96625</t>
-        </is>
+      <c r="AN104" t="n">
+        <v>13.062</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>12.96625</v>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
@@ -40872,15 +40460,11 @@
           <t>13.0275</t>
         </is>
       </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>13.075</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>12.96875</t>
-        </is>
+      <c r="AN105" t="n">
+        <v>13.075</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>12.96875</v>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
@@ -41259,15 +40843,11 @@
           <t>13.0175</t>
         </is>
       </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>13.083</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>12.9675</t>
-        </is>
+      <c r="AN106" t="n">
+        <v>13.083</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>12.9675</v>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
@@ -41646,15 +41226,11 @@
           <t>13.0075</t>
         </is>
       </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>13.087</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>12.96375</t>
-        </is>
+      <c r="AN107" t="n">
+        <v>13.087</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>12.96375</v>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
@@ -42033,15 +41609,11 @@
           <t>12.995</t>
         </is>
       </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>13.087</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>12.958125</t>
-        </is>
+      <c r="AN108" t="n">
+        <v>13.087</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>12.958125</v>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
@@ -42420,15 +41992,11 @@
           <t>12.97</t>
         </is>
       </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>13.082</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>12.951875</t>
-        </is>
+      <c r="AN109" t="n">
+        <v>13.082</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>12.951875</v>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
@@ -42807,15 +42375,11 @@
           <t>12.955</t>
         </is>
       </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>13.079</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>12.945625</t>
-        </is>
+      <c r="AN110" t="n">
+        <v>13.079</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>12.945625</v>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
@@ -43194,15 +42758,11 @@
           <t>12.94</t>
         </is>
       </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>13.08</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>12.9425</t>
-        </is>
+      <c r="AN111" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>12.9425</v>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
@@ -43581,15 +43141,11 @@
           <t>41.22000000000001</t>
         </is>
       </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>41.115</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>39.63</t>
-        </is>
+      <c r="AN112" t="n">
+        <v>41.115</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>39.63</v>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
@@ -43968,15 +43524,11 @@
           <t>41.13</t>
         </is>
       </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>41.08599999999999</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>39.56125</t>
-        </is>
+      <c r="AN113" t="n">
+        <v>41.08599999999999</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>39.56125</v>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
@@ -44355,15 +43907,11 @@
           <t>41.0425</t>
         </is>
       </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>41.037</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>39.50875</t>
-        </is>
+      <c r="AN114" t="n">
+        <v>41.037</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>39.50875</v>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
@@ -44742,15 +44290,11 @@
           <t>41.04000000000001</t>
         </is>
       </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>40.995</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>39.4825</t>
-        </is>
+      <c r="AN115" t="n">
+        <v>40.995</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>39.4825</v>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
@@ -45129,15 +44673,11 @@
           <t>40.975</t>
         </is>
       </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>40.931</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>39.449375</t>
-        </is>
+      <c r="AN116" t="n">
+        <v>40.931</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>39.449375</v>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
@@ -45516,15 +45056,11 @@
           <t>40.8925</t>
         </is>
       </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>40.877</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>39.41375</t>
-        </is>
+      <c r="AN117" t="n">
+        <v>40.877</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>39.41375</v>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
@@ -45903,15 +45439,11 @@
           <t>40.85</t>
         </is>
       </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>40.873</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>39.378125</t>
-        </is>
+      <c r="AN118" t="n">
+        <v>40.873</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>39.378125</v>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
@@ -46290,15 +45822,11 @@
           <t>40.77</t>
         </is>
       </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>40.87</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>39.3375</t>
-        </is>
+      <c r="AN119" t="n">
+        <v>40.87</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>39.3375</v>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
@@ -46677,15 +46205,11 @@
           <t>40.685</t>
         </is>
       </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>40.875</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>39.29</t>
-        </is>
+      <c r="AN120" t="n">
+        <v>40.875</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>39.29</v>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
@@ -47064,15 +46588,11 @@
           <t>40.5775</t>
         </is>
       </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>40.821</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>39.231875</t>
-        </is>
+      <c r="AN121" t="n">
+        <v>40.821</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>39.231875</v>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
@@ -47451,15 +46971,11 @@
           <t>31.4925</t>
         </is>
       </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>30.555</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>29.26375</t>
-        </is>
+      <c r="AN122" t="n">
+        <v>30.555</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>29.26375</v>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
@@ -47838,15 +47354,11 @@
           <t>31.44</t>
         </is>
       </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>30.491</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>29.169375</t>
-        </is>
+      <c r="AN123" t="n">
+        <v>30.491</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>29.169375</v>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
@@ -48225,15 +47737,11 @@
           <t>31.3975</t>
         </is>
       </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>30.418</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>29.085625</t>
-        </is>
+      <c r="AN124" t="n">
+        <v>30.418</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>29.085625</v>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
@@ -48612,15 +48120,11 @@
           <t>31.44</t>
         </is>
       </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>30.384</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>29.015</t>
-        </is>
+      <c r="AN125" t="n">
+        <v>30.384</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>29.015</v>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
@@ -48999,15 +48503,11 @@
           <t>31.295</t>
         </is>
       </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>30.28</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>28.930625</t>
-        </is>
+      <c r="AN126" t="n">
+        <v>30.28</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>28.930625</v>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
@@ -49386,15 +48886,11 @@
           <t>31.2</t>
         </is>
       </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>30.198</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>28.86125</t>
-        </is>
+      <c r="AN127" t="n">
+        <v>30.198</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>28.86125</v>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
@@ -49773,15 +49269,11 @@
           <t>31.205</t>
         </is>
       </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>30.141</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>28.80625</t>
-        </is>
+      <c r="AN128" t="n">
+        <v>30.141</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>28.80625</v>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
@@ -50160,15 +49652,11 @@
           <t>31.1325</t>
         </is>
       </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>30.068</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>28.75</t>
-        </is>
+      <c r="AN129" t="n">
+        <v>30.068</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>28.75</v>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
@@ -50547,15 +50035,11 @@
           <t>31.055</t>
         </is>
       </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>29.995</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>28.686875</t>
-        </is>
+      <c r="AN130" t="n">
+        <v>29.995</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>28.686875</v>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
@@ -50934,15 +50418,11 @@
           <t>30.975</t>
         </is>
       </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>29.918</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>28.6175</t>
-        </is>
+      <c r="AN131" t="n">
+        <v>29.918</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>28.6175</v>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
@@ -51321,15 +50801,11 @@
           <t>29.16</t>
         </is>
       </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>25.584</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>23.935</t>
-        </is>
+      <c r="AN132" t="n">
+        <v>25.584</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>23.935</v>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
@@ -51708,15 +51184,11 @@
           <t>28.9625</t>
         </is>
       </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>25.459</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>23.815</t>
-        </is>
+      <c r="AN133" t="n">
+        <v>25.459</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>23.815</v>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
@@ -52095,15 +51567,11 @@
           <t>28.685</t>
         </is>
       </c>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>25.306</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>23.690625</t>
-        </is>
+      <c r="AN134" t="n">
+        <v>25.306</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>23.690625</v>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
@@ -52482,15 +51950,11 @@
           <t>28.475</t>
         </is>
       </c>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>25.158</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>23.578125</t>
-        </is>
+      <c r="AN135" t="n">
+        <v>25.158</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>23.578125</v>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
@@ -52869,15 +52333,11 @@
           <t>28.12</t>
         </is>
       </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>24.977</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>23.454375</t>
-        </is>
+      <c r="AN136" t="n">
+        <v>24.977</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>23.454375</v>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
@@ -53256,15 +52716,11 @@
           <t>27.8</t>
         </is>
       </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>24.801</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>23.340625</t>
-        </is>
+      <c r="AN137" t="n">
+        <v>24.801</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>23.340625</v>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
@@ -53643,15 +53099,11 @@
           <t>27.5475</t>
         </is>
       </c>
-      <c r="AN138" t="inlineStr">
-        <is>
-          <t>24.641</t>
-        </is>
-      </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>23.241875</t>
-        </is>
+      <c r="AN138" t="n">
+        <v>24.641</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>23.241875</v>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
@@ -54030,15 +53482,11 @@
           <t>27.2225</t>
         </is>
       </c>
-      <c r="AN139" t="inlineStr">
-        <is>
-          <t>24.473</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>23.13625</t>
-        </is>
+      <c r="AN139" t="n">
+        <v>24.473</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>23.13625</v>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
@@ -54417,15 +53865,11 @@
           <t>26.8925</t>
         </is>
       </c>
-      <c r="AN140" t="inlineStr">
-        <is>
-          <t>24.315</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>23.03625</t>
-        </is>
+      <c r="AN140" t="n">
+        <v>24.315</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>23.03625</v>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
@@ -54804,15 +54248,11 @@
           <t>26.4975</t>
         </is>
       </c>
-      <c r="AN141" t="inlineStr">
-        <is>
-          <t>24.134</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>22.92</t>
-        </is>
+      <c r="AN141" t="n">
+        <v>24.134</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>22.92</v>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
@@ -55191,15 +54631,11 @@
           <t>24.8225</t>
         </is>
       </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>24.768</t>
-        </is>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>24.863125</t>
-        </is>
+      <c r="AN142" t="n">
+        <v>24.768</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>24.863125</v>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
@@ -55578,15 +55014,11 @@
           <t>24.84</t>
         </is>
       </c>
-      <c r="AN143" t="inlineStr">
-        <is>
-          <t>24.773</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>24.874375</t>
-        </is>
+      <c r="AN143" t="n">
+        <v>24.773</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>24.874375</v>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
@@ -55965,15 +55397,11 @@
           <t>24.845</t>
         </is>
       </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>24.774</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>24.881875</t>
-        </is>
+      <c r="AN144" t="n">
+        <v>24.774</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>24.881875</v>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
@@ -56352,15 +55780,11 @@
           <t>24.8575</t>
         </is>
       </c>
-      <c r="AN145" t="inlineStr">
-        <is>
-          <t>24.776</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>24.889375</t>
-        </is>
+      <c r="AN145" t="n">
+        <v>24.776</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>24.889375</v>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
@@ -56739,15 +56163,11 @@
           <t>24.86</t>
         </is>
       </c>
-      <c r="AN146" t="inlineStr">
-        <is>
-          <t>24.771</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>24.89625</t>
-        </is>
+      <c r="AN146" t="n">
+        <v>24.771</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>24.89625</v>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
@@ -57126,15 +56546,11 @@
           <t>24.855</t>
         </is>
       </c>
-      <c r="AN147" t="inlineStr">
-        <is>
-          <t>24.764</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>24.90375</t>
-        </is>
+      <c r="AN147" t="n">
+        <v>24.764</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>24.90375</v>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
@@ -57513,15 +56929,11 @@
           <t>24.855</t>
         </is>
       </c>
-      <c r="AN148" t="inlineStr">
-        <is>
-          <t>24.758</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>24.91</t>
-        </is>
+      <c r="AN148" t="n">
+        <v>24.758</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>24.91</v>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
@@ -57900,15 +57312,11 @@
           <t>24.855</t>
         </is>
       </c>
-      <c r="AN149" t="inlineStr">
-        <is>
-          <t>24.762</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>24.915625</t>
-        </is>
+      <c r="AN149" t="n">
+        <v>24.762</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>24.915625</v>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
@@ -58287,15 +57695,11 @@
           <t>24.86</t>
         </is>
       </c>
-      <c r="AN150" t="inlineStr">
-        <is>
-          <t>24.767</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>24.92</t>
-        </is>
+      <c r="AN150" t="n">
+        <v>24.767</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>24.92</v>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
@@ -58674,15 +58078,11 @@
           <t>24.8525</t>
         </is>
       </c>
-      <c r="AN151" t="inlineStr">
-        <is>
-          <t>24.772</t>
-        </is>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>24.92125</t>
-        </is>
+      <c r="AN151" t="n">
+        <v>24.772</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>24.92125</v>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
@@ -59061,15 +58461,11 @@
           <t>38.98</t>
         </is>
       </c>
-      <c r="AN152" t="inlineStr">
-        <is>
-          <t>39.279</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>39.199375</t>
-        </is>
+      <c r="AN152" t="n">
+        <v>39.279</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>39.199375</v>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
@@ -59448,15 +58844,11 @@
           <t>39.065</t>
         </is>
       </c>
-      <c r="AN153" t="inlineStr">
-        <is>
-          <t>39.337</t>
-        </is>
-      </c>
-      <c r="AO153" t="inlineStr">
-        <is>
-          <t>39.195</t>
-        </is>
+      <c r="AN153" t="n">
+        <v>39.337</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>39.195</v>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
@@ -59835,15 +59227,11 @@
           <t>39.105</t>
         </is>
       </c>
-      <c r="AN154" t="inlineStr">
-        <is>
-          <t>39.392</t>
-        </is>
-      </c>
-      <c r="AO154" t="inlineStr">
-        <is>
-          <t>39.18875</t>
-        </is>
+      <c r="AN154" t="n">
+        <v>39.392</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>39.18875</v>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
@@ -60222,15 +59610,11 @@
           <t>39.18</t>
         </is>
       </c>
-      <c r="AN155" t="inlineStr">
-        <is>
-          <t>39.43</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>39.194375</t>
-        </is>
+      <c r="AN155" t="n">
+        <v>39.43</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>39.194375</v>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
@@ -60609,15 +59993,11 @@
           <t>39.21</t>
         </is>
       </c>
-      <c r="AN156" t="inlineStr">
-        <is>
-          <t>39.435</t>
-        </is>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>39.19125</t>
-        </is>
+      <c r="AN156" t="n">
+        <v>39.435</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>39.19125</v>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
@@ -60996,15 +60376,11 @@
           <t>39.245</t>
         </is>
       </c>
-      <c r="AN157" t="inlineStr">
-        <is>
-          <t>39.428</t>
-        </is>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>39.18875</t>
-        </is>
+      <c r="AN157" t="n">
+        <v>39.428</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>39.18875</v>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
@@ -61383,15 +60759,11 @@
           <t>39.2625</t>
         </is>
       </c>
-      <c r="AN158" t="inlineStr">
-        <is>
-          <t>39.429</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>39.185</t>
-        </is>
+      <c r="AN158" t="n">
+        <v>39.429</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>39.185</v>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
@@ -61770,15 +61142,11 @@
           <t>39.255</t>
         </is>
       </c>
-      <c r="AN159" t="inlineStr">
-        <is>
-          <t>39.438</t>
-        </is>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>39.188125</t>
-        </is>
+      <c r="AN159" t="n">
+        <v>39.438</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>39.188125</v>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
@@ -62157,15 +61525,11 @@
           <t>39.275</t>
         </is>
       </c>
-      <c r="AN160" t="inlineStr">
-        <is>
-          <t>39.451</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>39.19500000000001</t>
-        </is>
+      <c r="AN160" t="n">
+        <v>39.451</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>39.19500000000001</v>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
@@ -62544,15 +61908,11 @@
           <t>39.3175</t>
         </is>
       </c>
-      <c r="AN161" t="inlineStr">
-        <is>
-          <t>39.47</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>39.20625</t>
-        </is>
+      <c r="AN161" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>39.20625</v>
       </c>
       <c r="AP161" t="inlineStr">
         <is>

--- a/Result/checksun/電器電纜.xlsx
+++ b/Result/checksun/電器電纜.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1725,7 +1725,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2151,7 +2151,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2577,7 +2577,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3003,7 +3003,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3427,7 +3427,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>5283</t>
@@ -3849,7 +3853,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>5283</t>
@@ -4271,7 +4279,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>5283</t>
@@ -5547,7 +5559,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5975,7 +5987,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6401,7 +6413,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>4930</t>
@@ -6825,7 +6841,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>4930</t>
@@ -7249,7 +7269,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>4930</t>
@@ -7673,7 +7697,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>4930</t>
@@ -8097,7 +8125,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>4930</t>
@@ -10235,7 +10267,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>價_量;【d1】;【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10659,7 +10691,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>2061</t>
@@ -11081,7 +11117,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>2061</t>
@@ -19599,7 +19639,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20029,7 +20069,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20459,7 +20499,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -20887,7 +20927,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>1618</t>
@@ -21313,7 +21357,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>1618</t>
@@ -21739,7 +21787,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>1618</t>
@@ -22165,7 +22217,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>1618</t>
@@ -24311,7 +24367,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>1617</t>
@@ -24736,7 +24796,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>1617</t>
@@ -25161,7 +25225,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>1617</t>
@@ -25586,7 +25654,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>1617</t>
@@ -29014,7 +29086,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>1616</t>
@@ -29436,7 +29512,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>1616</t>
@@ -29858,7 +29938,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>1616</t>
@@ -30280,7 +30364,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>1616</t>
@@ -30702,7 +30790,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>1616</t>
@@ -31124,7 +31216,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>1616</t>
@@ -31546,7 +31642,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>1616</t>
@@ -36248,7 +36348,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -36677,7 +36777,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37106,7 +37206,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -37535,7 +37635,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -37964,7 +38064,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38393,7 +38493,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -38826,7 +38926,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39259,7 +39359,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -39692,7 +39792,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40125,7 +40225,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -40558,7 +40658,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -40989,7 +41089,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>1614</t>
@@ -41418,7 +41522,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>1614</t>
@@ -41847,7 +41955,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>1614</t>
@@ -42276,7 +42388,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>1614</t>
@@ -42705,7 +42821,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>1614</t>
@@ -43134,7 +43254,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr"/>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>1612</t>
@@ -43559,7 +43683,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>1612</t>
@@ -43984,7 +44112,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>1612</t>
@@ -44409,7 +44541,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>1612</t>
@@ -44834,7 +44970,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>1612</t>
@@ -47835,7 +47975,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -48265,7 +48405,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -48695,7 +48835,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49125,7 +49265,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -49555,7 +49695,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -49985,7 +50125,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -50413,7 +50553,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>1611</t>
@@ -50839,7 +50983,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>1611</t>
@@ -51265,7 +51413,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>1611</t>
@@ -52553,7 +52705,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -52982,7 +53134,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -53409,7 +53561,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>1609</t>
@@ -53834,7 +53990,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>1609</t>
@@ -54259,7 +54419,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>1609</t>
@@ -66764,7 +66928,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -67191,7 +67355,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -67618,7 +67782,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -68045,7 +68209,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -68472,7 +68636,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -68899,7 +69063,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -69324,7 +69488,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr"/>
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>1604</t>
@@ -69747,7 +69915,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr"/>
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>1604</t>
@@ -70170,7 +70342,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr"/>
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>1604</t>
@@ -71447,7 +71623,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr"/>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>1603</t>
@@ -71872,7 +72052,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr"/>
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>1603</t>
@@ -72297,7 +72481,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr"/>
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>1603</t>
@@ -72722,7 +72910,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr"/>
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>1603</t>
@@ -73147,7 +73339,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr"/>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>1603</t>
@@ -73572,7 +73768,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr"/>
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>1603</t>
@@ -73997,7 +74197,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr"/>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>1603</t>
@@ -74422,7 +74626,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr"/>
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>1603</t>
